--- a/docs/HOR Ieviešanas tāme.xlsx
+++ b/docs/HOR Ieviešanas tāme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raivis.Biskaps\Documents\Claude\Projects\Horizon pārdošana\docs-qa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB94077-5A56-4917-89A9-9750C1F9CBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8205470-F6FD-492C-B9F1-723003A9660D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
   <si>
     <t>Darba veids</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Pakalpojuma abonēšana</t>
-  </si>
-  <si>
-    <t>Bāze</t>
   </si>
   <si>
     <t>Izpēte un konfigurācija. Ieviešanai tiek izmantota sistēmas sākuma konfigurācija, kas jau iekļauj visbiežāk sastopamo pamata konfigurāciju. Projekta ietvaros tiek veikta izpēte, lai identificētu uzņēmuma specifiskos procesus, kuriem nepieciešama sākuma konfigurācijas papildināšana.  Izpētes ietvaros tiek izrunāts, kādas analītiskās dimensijas vai klasifikatori būtu jāizmanto, lai nodrošinātu uzņēmuma analītikas atskaites. Tiek identificēts, vai ir kādi biznesa pamata procesi, kuriem nepieciešama konfigurācijas pielāgošana, veidojami dokumenti tipi, kontējumu shēmas, uzstādījumi. Piemēram, specifisks rēķinu izrakstīšanas process, PVN uzskaite, noliktavas/krājumu uzskaite, projektu uzskaite u.c.</t>
@@ -300,10 +297,25 @@
     <t/>
   </si>
   <si>
-    <t>Horizon modulis</t>
-  </si>
-  <si>
     <t>Instalācija</t>
+  </si>
+  <si>
+    <t>Horizon sadaļa</t>
+  </si>
+  <si>
+    <t>Pamatsistēma</t>
+  </si>
+  <si>
+    <t>Modulis</t>
+  </si>
+  <si>
+    <t>Personāls</t>
+  </si>
+  <si>
+    <t>Grāmatvedība +</t>
+  </si>
+  <si>
+    <t>Numo</t>
   </si>
 </sst>
 </file>
@@ -421,7 +433,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -620,11 +632,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFE0E8EC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -734,6 +757,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,623 +1101,694 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.109375" customWidth="1"/>
-    <col min="2" max="2" width="63.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" customWidth="1"/>
+    <col min="1" max="2" width="28.109375" customWidth="1"/>
+    <col min="3" max="3" width="63.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72.599999999999994" thickTop="1">
+    <row r="1" spans="1:8" ht="57.6" thickTop="1">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="33" customHeight="1">
+      <c r="A2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="195">
+      <c r="A3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="13">
+        <v>1600</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.6">
+      <c r="A4" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11">
+        <v>80</v>
+      </c>
+      <c r="G4" s="13">
+        <v>240</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="165">
+      <c r="A5" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="19">
+        <v>8</v>
+      </c>
+      <c r="F5" s="11">
+        <v>80</v>
+      </c>
+      <c r="G5" s="13">
+        <v>640</v>
+      </c>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="45">
+      <c r="A6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="11">
+        <v>80</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="75">
+      <c r="A7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="19">
+        <v>8</v>
+      </c>
+      <c r="F7" s="11">
+        <v>80</v>
+      </c>
+      <c r="G7" s="13">
+        <v>640</v>
+      </c>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" ht="62.4">
+      <c r="A8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28">
+        <v>960</v>
+      </c>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6">
+      <c r="A9" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="29">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F9" s="30">
+        <v>80</v>
+      </c>
+      <c r="G9" s="28">
+        <v>160</v>
+      </c>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" ht="31.2">
+      <c r="A10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="29">
+        <v>10</v>
+      </c>
+      <c r="F10" s="30">
+        <v>80</v>
+      </c>
+      <c r="G10" s="28">
+        <v>800</v>
+      </c>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" ht="46.8">
+      <c r="A11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="29">
+        <v>5</v>
+      </c>
+      <c r="F11" s="30">
+        <v>80</v>
+      </c>
+      <c r="G11" s="28">
+        <v>400</v>
+      </c>
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" spans="1:8" ht="46.8">
+      <c r="A12" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="29">
+        <v>5</v>
+      </c>
+      <c r="F12" s="30">
+        <v>80</v>
+      </c>
+      <c r="G12" s="28">
+        <v>400</v>
+      </c>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="1:8" ht="345">
+      <c r="A13" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="13">
+        <v>1920</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="31.2">
+      <c r="A14" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="11">
+        <v>80</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="180">
+      <c r="A15" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="13">
+        <v>1920</v>
+      </c>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="31.2">
+      <c r="A16" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="19">
         <v>3</v>
       </c>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" spans="1:7" ht="33" customHeight="1">
-      <c r="A2" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="F16" s="11">
+        <v>80</v>
+      </c>
+      <c r="G16" s="13">
+        <v>240</v>
+      </c>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="210">
+      <c r="A17" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="13">
+        <v>480</v>
+      </c>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="31.2">
+      <c r="A18" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="11">
+        <v>80</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="78">
+      <c r="A19" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="13">
+        <v>240</v>
+      </c>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="31.2">
+      <c r="A20" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="19"/>
+      <c r="F20" s="11">
+        <v>80</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="315">
+      <c r="A21" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="13">
+        <v>2320</v>
+      </c>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="31.2">
+      <c r="A22" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="11">
+        <v>80</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="120">
+      <c r="A23" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="13">
+        <v>1920</v>
+      </c>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.6">
+      <c r="A24" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="11">
+        <v>80</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="150">
+      <c r="A25" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="13">
+        <v>1600</v>
+      </c>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" ht="30">
+      <c r="A26" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="19">
         <v>4</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" ht="195">
-      <c r="A3" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="F26" s="11">
+        <v>80</v>
+      </c>
+      <c r="G26" s="13">
+        <v>320</v>
+      </c>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="75">
+      <c r="A27" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="13">
-        <v>1600</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.6">
-      <c r="A4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="19">
-        <v>3</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="E27" s="16"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" ht="120">
+      <c r="A28" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="13">
+        <v>1360</v>
+      </c>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="31.2">
+      <c r="A29" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="13">
+        <v>320</v>
+      </c>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="105">
+      <c r="A30" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="19"/>
+      <c r="F30" s="11">
         <v>80</v>
       </c>
-      <c r="F4" s="13">
-        <v>240</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7" ht="165">
-      <c r="A5" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="19">
-        <v>8</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="G30" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" ht="39" customHeight="1" thickBot="1">
+      <c r="A31" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="35"/>
+      <c r="F31" s="36">
         <v>80</v>
       </c>
-      <c r="F5" s="13">
-        <v>640</v>
-      </c>
-      <c r="G5" s="20"/>
-    </row>
-    <row r="6" spans="1:7" ht="45">
-      <c r="A6" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="11">
-        <v>80</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="20"/>
-    </row>
-    <row r="7" spans="1:7" ht="75">
-      <c r="A7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="19">
-        <v>8</v>
-      </c>
-      <c r="E7" s="11">
-        <v>80</v>
-      </c>
-      <c r="F7" s="13">
-        <v>640</v>
-      </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" ht="62.4">
-      <c r="A8" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28">
-        <v>960</v>
-      </c>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6">
-      <c r="A9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="29">
-        <v>2</v>
-      </c>
-      <c r="E9" s="30">
-        <v>80</v>
-      </c>
-      <c r="F9" s="28">
-        <v>160</v>
-      </c>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7" ht="31.2">
-      <c r="A10" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="29">
-        <v>10</v>
-      </c>
-      <c r="E10" s="30">
-        <v>80</v>
-      </c>
-      <c r="F10" s="28">
-        <v>800</v>
-      </c>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" ht="46.8">
-      <c r="A11" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="29">
-        <v>5</v>
-      </c>
-      <c r="E11" s="30">
-        <v>80</v>
-      </c>
-      <c r="F11" s="28">
-        <v>400</v>
-      </c>
-      <c r="G11" s="20"/>
-    </row>
-    <row r="12" spans="1:7" ht="46.8">
-      <c r="A12" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="29">
-        <v>5</v>
-      </c>
-      <c r="E12" s="30">
-        <v>80</v>
-      </c>
-      <c r="F12" s="28">
-        <v>400</v>
-      </c>
-      <c r="G12" s="20"/>
-    </row>
-    <row r="13" spans="1:7" ht="345">
-      <c r="A13" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="13">
-        <v>1920</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="31.2">
-      <c r="A14" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="11">
-        <v>80</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" ht="180">
-      <c r="A15" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="13">
-        <v>1920</v>
-      </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" ht="31.2">
-      <c r="A16" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="19">
-        <v>3</v>
-      </c>
-      <c r="E16" s="11">
-        <v>80</v>
-      </c>
-      <c r="F16" s="13">
-        <v>240</v>
-      </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="210">
-      <c r="A17" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="13">
-        <v>480</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="31.2">
-      <c r="A18" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="11">
-        <v>80</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="78">
-      <c r="A19" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="13">
-        <v>240</v>
-      </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" ht="31.2">
-      <c r="A20" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="11">
-        <v>80</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="315">
-      <c r="A21" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="13">
-        <v>2320</v>
-      </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="31.2">
-      <c r="A22" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="11">
-        <v>80</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="120">
-      <c r="A23" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="13">
-        <v>1920</v>
-      </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.6">
-      <c r="A24" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="11">
-        <v>80</v>
-      </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" ht="150">
-      <c r="A25" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="13">
-        <v>1600</v>
-      </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" ht="30">
-      <c r="A26" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="19">
-        <v>4</v>
-      </c>
-      <c r="E26" s="11">
-        <v>80</v>
-      </c>
-      <c r="F26" s="13">
-        <v>320</v>
-      </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" ht="75">
-      <c r="A27" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" ht="120">
-      <c r="A28" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="13">
-        <v>1360</v>
-      </c>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="31.2">
-      <c r="A29" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="13">
-        <v>320</v>
-      </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" ht="105">
-      <c r="A30" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="11">
-        <v>80</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" ht="39" customHeight="1" thickBot="1">
-      <c r="A31" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="36">
-        <v>80</v>
-      </c>
-      <c r="F31" s="37"/>
-      <c r="G31" s="23"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.6">
+      <c r="G31" s="37"/>
+      <c r="H31" s="23"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.6">
       <c r="A32" s="38"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="40"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="1"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="C3:C26" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D3:D26" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Gabaldarbs,Pēc fakta"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showInputMessage="1" prompt="Noklikšķiniet un ievadiet vērtību no diapazons PZA!A3:A4" sqref="D27:D30" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" showInputMessage="1" prompt="Noklikšķiniet un ievadiet vērtību no diapazons PZA!A3:A4" xr:uid="{00000000-0002-0000-0000-000002000000}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>C27:C30</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>